--- a/src/main/resources/documents/2026/prijedlozi BO/predsjednici/predsjednici kontakt.xlsx
+++ b/src/main/resources/documents/2026/prijedlozi BO/predsjednici/predsjednici kontakt.xlsx
@@ -1209,10 +1209,26 @@
           <t>Замjеник предсjедника</t>
         </is>
       </c>
-      <c r="C22" s="26" t="n"/>
-      <c r="D22" s="26" t="n"/>
-      <c r="E22" s="26" t="n"/>
-      <c r="F22" s="26" t="n"/>
+      <c r="C22" s="26" t="inlineStr">
+        <is>
+          <t>2304981105067</t>
+        </is>
+      </c>
+      <c r="D22" s="26" t="inlineStr">
+        <is>
+          <t>ДУШКА</t>
+        </is>
+      </c>
+      <c r="E22" s="26" t="inlineStr">
+        <is>
+          <t>ОЗРЕН</t>
+        </is>
+      </c>
+      <c r="F22" s="26" t="inlineStr">
+        <is>
+          <t>065/682-963</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="26" t="inlineStr">
@@ -3531,22 +3547,22 @@
       </c>
       <c r="C99" s="26" t="inlineStr">
         <is>
-          <t>1002000105003</t>
+          <t>1408980105019</t>
         </is>
       </c>
       <c r="D99" s="26" t="inlineStr">
         <is>
-          <t>ДАJАНА</t>
+          <t>ЖАНА</t>
         </is>
       </c>
       <c r="E99" s="26" t="inlineStr">
         <is>
-          <t>ЂУКИЋ</t>
+          <t>БАБИЋ</t>
         </is>
       </c>
       <c r="F99" s="26" t="inlineStr">
         <is>
-          <t>066/818-877</t>
+          <t>066/788-888</t>
         </is>
       </c>
     </row>
@@ -3563,22 +3579,22 @@
       </c>
       <c r="C100" s="26" t="inlineStr">
         <is>
-          <t>2804963100034</t>
+          <t>1002000105003</t>
         </is>
       </c>
       <c r="D100" s="26" t="inlineStr">
         <is>
-          <t>ДРАШКО</t>
+          <t>ДАJАНА</t>
         </is>
       </c>
       <c r="E100" s="26" t="inlineStr">
         <is>
-          <t>ПЕJИЋ</t>
+          <t>ЂУКИЋ</t>
         </is>
       </c>
       <c r="F100" s="26" t="inlineStr">
         <is>
-          <t>065/342-002</t>
+          <t>066/818-877</t>
         </is>
       </c>
     </row>
@@ -5896,7 +5912,11 @@
           <t>БАJИЧИЋ</t>
         </is>
       </c>
-      <c r="F175" s="26" t="n"/>
+      <c r="F175" s="26" t="inlineStr">
+        <is>
+          <t>065/875-852</t>
+        </is>
+      </c>
     </row>
     <row r="176" ht="18" customHeight="1">
       <c r="A176" s="26" t="inlineStr">
@@ -8935,22 +8955,22 @@
       </c>
       <c r="C273" s="26" t="inlineStr">
         <is>
-          <t>1408980105019</t>
+          <t>1704957170006</t>
         </is>
       </c>
       <c r="D273" s="26" t="inlineStr">
         <is>
-          <t>ЖАНА</t>
+          <t>ХАЏИ МИЛЕНКО</t>
         </is>
       </c>
       <c r="E273" s="26" t="inlineStr">
         <is>
-          <t>БАБИЋ</t>
+          <t>ГАВРИЋ</t>
         </is>
       </c>
       <c r="F273" s="26" t="inlineStr">
         <is>
-          <t>066/788-888</t>
+          <t>065/474-121</t>
         </is>
       </c>
     </row>
@@ -9413,26 +9433,10 @@
           <t>Замjеник предсjедника</t>
         </is>
       </c>
-      <c r="C288" s="26" t="inlineStr">
-        <is>
-          <t>1704957170006</t>
-        </is>
-      </c>
-      <c r="D288" s="26" t="inlineStr">
-        <is>
-          <t>ХАЏИ МИЛЕНКО</t>
-        </is>
-      </c>
-      <c r="E288" s="26" t="inlineStr">
-        <is>
-          <t>ГАВРИЋ</t>
-        </is>
-      </c>
-      <c r="F288" s="26" t="inlineStr">
-        <is>
-          <t>065/474-121</t>
-        </is>
-      </c>
+      <c r="C288" s="26" t="n"/>
+      <c r="D288" s="26" t="n"/>
+      <c r="E288" s="26" t="n"/>
+      <c r="F288" s="26" t="n"/>
     </row>
     <row r="289" ht="18" customHeight="1">
       <c r="A289" s="26" t="inlineStr">
@@ -11335,22 +11339,22 @@
       </c>
       <c r="C351" s="26" t="inlineStr">
         <is>
-          <t>2409974107085</t>
+          <t>2804963100034</t>
         </is>
       </c>
       <c r="D351" s="26" t="inlineStr">
         <is>
-          <t>ДРАГАНА</t>
+          <t>ДРАШКО</t>
         </is>
       </c>
       <c r="E351" s="26" t="inlineStr">
         <is>
-          <t>АЋИЋ</t>
+          <t>ПЕJИЋ</t>
         </is>
       </c>
       <c r="F351" s="26" t="inlineStr">
         <is>
-          <t>065/603-179</t>
+          <t>065/342-002</t>
         </is>
       </c>
     </row>
@@ -14037,10 +14041,26 @@
           <t>Предсjедник</t>
         </is>
       </c>
-      <c r="C439" s="26" t="n"/>
-      <c r="D439" s="26" t="n"/>
-      <c r="E439" s="26" t="n"/>
-      <c r="F439" s="26" t="n"/>
+      <c r="C439" s="26" t="inlineStr">
+        <is>
+          <t>0907992105017</t>
+        </is>
+      </c>
+      <c r="D439" s="26" t="inlineStr">
+        <is>
+          <t>ВАЊА</t>
+        </is>
+      </c>
+      <c r="E439" s="26" t="inlineStr">
+        <is>
+          <t>JОВАНИЋ</t>
+        </is>
+      </c>
+      <c r="F439" s="26" t="inlineStr">
+        <is>
+          <t>065/001-001</t>
+        </is>
+      </c>
     </row>
     <row r="440" ht="18" customHeight="1">
       <c r="A440" s="26" t="inlineStr">
@@ -14053,26 +14073,10 @@
           <t>Замjеник предсjедника</t>
         </is>
       </c>
-      <c r="C440" s="26" t="inlineStr">
-        <is>
-          <t>0907992105017</t>
-        </is>
-      </c>
-      <c r="D440" s="26" t="inlineStr">
-        <is>
-          <t>ВАЊА</t>
-        </is>
-      </c>
-      <c r="E440" s="26" t="inlineStr">
-        <is>
-          <t>JОВАНИЋ</t>
-        </is>
-      </c>
-      <c r="F440" s="26" t="inlineStr">
-        <is>
-          <t>065/001-001</t>
-        </is>
-      </c>
+      <c r="C440" s="26" t="n"/>
+      <c r="D440" s="26" t="n"/>
+      <c r="E440" s="26" t="n"/>
+      <c r="F440" s="26" t="n"/>
     </row>
     <row r="441" ht="18" customHeight="1">
       <c r="A441" s="26" t="inlineStr">
@@ -16081,9 +16085,21 @@
           <t>Замjеник предсjедника</t>
         </is>
       </c>
-      <c r="C508" s="26" t="n"/>
-      <c r="D508" s="26" t="n"/>
-      <c r="E508" s="26" t="n"/>
+      <c r="C508" s="26" t="inlineStr">
+        <is>
+          <t>0802983105016</t>
+        </is>
+      </c>
+      <c r="D508" s="26" t="inlineStr">
+        <is>
+          <t>ДРАГАНА</t>
+        </is>
+      </c>
+      <c r="E508" s="26" t="inlineStr">
+        <is>
+          <t>МАСТАЛИЦА</t>
+        </is>
+      </c>
       <c r="F508" s="26" t="n"/>
     </row>
     <row r="509" ht="18" customHeight="1">

--- a/src/main/resources/documents/2026/prijedlozi BO/predsjednici/predsjednici kontakt.xlsx
+++ b/src/main/resources/documents/2026/prijedlozi BO/predsjednici/predsjednici kontakt.xlsx
@@ -665,26 +665,10 @@
           <t>Замjеник предсjедника</t>
         </is>
       </c>
-      <c r="C4" s="26" t="inlineStr">
-        <is>
-          <t>1605981115034</t>
-        </is>
-      </c>
-      <c r="D4" s="26" t="inlineStr">
-        <is>
-          <t>МАРИJАНА</t>
-        </is>
-      </c>
-      <c r="E4" s="26" t="inlineStr">
-        <is>
-          <t>ПРПА РАДУН</t>
-        </is>
-      </c>
-      <c r="F4" s="26" t="inlineStr">
-        <is>
-          <t>065/336-672</t>
-        </is>
-      </c>
+      <c r="C4" s="26" t="n"/>
+      <c r="D4" s="26" t="n"/>
+      <c r="E4" s="26" t="n"/>
+      <c r="F4" s="26" t="n"/>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="26" t="inlineStr">
@@ -793,26 +777,10 @@
           <t>Замjеник предсjедника</t>
         </is>
       </c>
-      <c r="C8" s="26" t="inlineStr">
-        <is>
-          <t>0612986125006</t>
-        </is>
-      </c>
-      <c r="D8" s="26" t="inlineStr">
-        <is>
-          <t>МАРJАНА</t>
-        </is>
-      </c>
-      <c r="E8" s="26" t="inlineStr">
-        <is>
-          <t>МАЛБАШИЋ</t>
-        </is>
-      </c>
-      <c r="F8" s="26" t="inlineStr">
-        <is>
-          <t>066/130-828</t>
-        </is>
-      </c>
+      <c r="C8" s="26" t="n"/>
+      <c r="D8" s="26" t="n"/>
+      <c r="E8" s="26" t="n"/>
+      <c r="F8" s="26" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="26" t="inlineStr">
@@ -969,10 +937,26 @@
           <t>Замjеник предсjедника</t>
         </is>
       </c>
-      <c r="C14" s="26" t="n"/>
-      <c r="D14" s="26" t="n"/>
-      <c r="E14" s="26" t="n"/>
-      <c r="F14" s="26" t="n"/>
+      <c r="C14" s="26" t="inlineStr">
+        <is>
+          <t>1605981115034</t>
+        </is>
+      </c>
+      <c r="D14" s="26" t="inlineStr">
+        <is>
+          <t>МАРИJАНА</t>
+        </is>
+      </c>
+      <c r="E14" s="26" t="inlineStr">
+        <is>
+          <t>ПРПА РАДУН</t>
+        </is>
+      </c>
+      <c r="F14" s="26" t="inlineStr">
+        <is>
+          <t>065/336-672</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
@@ -1307,22 +1291,22 @@
       </c>
       <c r="C25" s="26" t="inlineStr">
         <is>
-          <t>1309973105005</t>
+          <t>2711996100031</t>
         </is>
       </c>
       <c r="D25" s="26" t="inlineStr">
         <is>
-          <t>НЕДА</t>
+          <t>СЕБАСТИJАН</t>
         </is>
       </c>
       <c r="E25" s="26" t="inlineStr">
         <is>
-          <t>СИМИЋ-ЖЕРАJИЋ</t>
+          <t>КАРАН</t>
         </is>
       </c>
       <c r="F25" s="26" t="inlineStr">
         <is>
-          <t>066/430-868</t>
+          <t>062/234-146</t>
         </is>
       </c>
     </row>
@@ -3594,7 +3578,7 @@
       </c>
       <c r="F100" s="26" t="inlineStr">
         <is>
-          <t>066/818-877</t>
+          <t>065/342-002</t>
         </is>
       </c>
     </row>
@@ -4537,10 +4521,26 @@
           <t>Замjеник предсjедника</t>
         </is>
       </c>
-      <c r="C130" s="26" t="n"/>
-      <c r="D130" s="26" t="n"/>
-      <c r="E130" s="26" t="n"/>
-      <c r="F130" s="26" t="n"/>
+      <c r="C130" s="26" t="inlineStr">
+        <is>
+          <t>1704987370409</t>
+        </is>
+      </c>
+      <c r="D130" s="26" t="inlineStr">
+        <is>
+          <t>ЖАРКО</t>
+        </is>
+      </c>
+      <c r="E130" s="26" t="inlineStr">
+        <is>
+          <t>ГРМУША</t>
+        </is>
+      </c>
+      <c r="F130" s="26" t="inlineStr">
+        <is>
+          <t>065/933-951</t>
+        </is>
+      </c>
     </row>
     <row r="131" ht="18" customHeight="1">
       <c r="A131" s="26" t="inlineStr">
@@ -4713,10 +4713,26 @@
           <t>Замjеник предсjедника</t>
         </is>
       </c>
-      <c r="C136" s="26" t="n"/>
-      <c r="D136" s="26" t="n"/>
-      <c r="E136" s="26" t="n"/>
-      <c r="F136" s="26" t="n"/>
+      <c r="C136" s="26" t="inlineStr">
+        <is>
+          <t>0705987330051</t>
+        </is>
+      </c>
+      <c r="D136" s="26" t="inlineStr">
+        <is>
+          <t>САША</t>
+        </is>
+      </c>
+      <c r="E136" s="26" t="inlineStr">
+        <is>
+          <t>ЂУРИЋ</t>
+        </is>
+      </c>
+      <c r="F136" s="26" t="inlineStr">
+        <is>
+          <t>065/459-838</t>
+        </is>
+      </c>
     </row>
     <row r="137" ht="18" customHeight="1">
       <c r="A137" s="26" t="inlineStr">
@@ -6955,22 +6971,22 @@
       </c>
       <c r="C208" s="26" t="inlineStr">
         <is>
-          <t>2711996100031</t>
+          <t>2802964143648</t>
         </is>
       </c>
       <c r="D208" s="26" t="inlineStr">
         <is>
-          <t>СЕБАСТИJАН</t>
+          <t>МИЛОJКО</t>
         </is>
       </c>
       <c r="E208" s="26" t="inlineStr">
         <is>
-          <t>КАРАН</t>
+          <t>БАБИЋ</t>
         </is>
       </c>
       <c r="F208" s="26" t="inlineStr">
         <is>
-          <t>062/234-146</t>
+          <t>065/789-765</t>
         </is>
       </c>
     </row>
@@ -9179,22 +9195,22 @@
       </c>
       <c r="C280" s="26" t="inlineStr">
         <is>
-          <t>1503987105041</t>
+          <t>2804963100034</t>
         </is>
       </c>
       <c r="D280" s="26" t="inlineStr">
         <is>
-          <t>СЕНАДА</t>
+          <t>ДРАШКО</t>
         </is>
       </c>
       <c r="E280" s="26" t="inlineStr">
         <is>
-          <t>МУХУРДАРЕВИЋ</t>
+          <t>ПЕJИЋ</t>
         </is>
       </c>
       <c r="F280" s="26" t="inlineStr">
         <is>
-          <t>065/729-751</t>
+          <t>065/342-002</t>
         </is>
       </c>
     </row>
@@ -10345,10 +10361,26 @@
           <t>Замjеник предсjедника</t>
         </is>
       </c>
-      <c r="C318" s="26" t="n"/>
-      <c r="D318" s="26" t="n"/>
-      <c r="E318" s="26" t="n"/>
-      <c r="F318" s="26" t="n"/>
+      <c r="C318" s="26" t="inlineStr">
+        <is>
+          <t>1104983100000</t>
+        </is>
+      </c>
+      <c r="D318" s="26" t="inlineStr">
+        <is>
+          <t>ДАЛИБОРКА</t>
+        </is>
+      </c>
+      <c r="E318" s="26" t="inlineStr">
+        <is>
+          <t>МИЈИЋ</t>
+        </is>
+      </c>
+      <c r="F318" s="26" t="inlineStr">
+        <is>
+          <t>065/219-081</t>
+        </is>
+      </c>
     </row>
     <row r="319" ht="18" customHeight="1">
       <c r="A319" s="26" t="inlineStr">
@@ -10393,10 +10425,26 @@
           <t>Замjеник предсjедника</t>
         </is>
       </c>
-      <c r="C320" s="26" t="n"/>
-      <c r="D320" s="26" t="n"/>
-      <c r="E320" s="26" t="n"/>
-      <c r="F320" s="26" t="n"/>
+      <c r="C320" s="26" t="inlineStr">
+        <is>
+          <t>0108969360042</t>
+        </is>
+      </c>
+      <c r="D320" s="26" t="inlineStr">
+        <is>
+          <t>ЗЛАТИБОР</t>
+        </is>
+      </c>
+      <c r="E320" s="26" t="inlineStr">
+        <is>
+          <t>МИЛИНОВИЋ</t>
+        </is>
+      </c>
+      <c r="F320" s="26" t="inlineStr">
+        <is>
+          <t>065/784-018</t>
+        </is>
+      </c>
     </row>
     <row r="321" ht="18" customHeight="1">
       <c r="A321" s="26" t="inlineStr">
@@ -11339,22 +11387,22 @@
       </c>
       <c r="C351" s="26" t="inlineStr">
         <is>
-          <t>2804963100034</t>
+          <t>1503987105041</t>
         </is>
       </c>
       <c r="D351" s="26" t="inlineStr">
         <is>
-          <t>ДРАШКО</t>
+          <t>СЕНАДА</t>
         </is>
       </c>
       <c r="E351" s="26" t="inlineStr">
         <is>
-          <t>ПЕJИЋ</t>
+          <t>МУХУРДАРЕВИЋ</t>
         </is>
       </c>
       <c r="F351" s="26" t="inlineStr">
         <is>
-          <t>065/342-002</t>
+          <t>065/729-751</t>
         </is>
       </c>
     </row>
@@ -11579,22 +11627,22 @@
       </c>
       <c r="C359" s="26" t="inlineStr">
         <is>
-          <t>1305993105022</t>
+          <t>0612986125006</t>
         </is>
       </c>
       <c r="D359" s="26" t="inlineStr">
         <is>
-          <t>ТАТJАНА</t>
+          <t>МАРJАНА</t>
         </is>
       </c>
       <c r="E359" s="26" t="inlineStr">
         <is>
-          <t>МАРКОВИЋ</t>
+          <t>МАЛБАШИЋ</t>
         </is>
       </c>
       <c r="F359" s="26" t="inlineStr">
         <is>
-          <t>066 358 945</t>
+          <t>066/310-828</t>
         </is>
       </c>
     </row>
@@ -15397,10 +15445,26 @@
           <t>Замjеник предсjедника</t>
         </is>
       </c>
-      <c r="C484" s="26" t="n"/>
-      <c r="D484" s="26" t="n"/>
-      <c r="E484" s="26" t="n"/>
-      <c r="F484" s="26" t="n"/>
+      <c r="C484" s="26" t="inlineStr">
+        <is>
+          <t>0108969360042</t>
+        </is>
+      </c>
+      <c r="D484" s="26" t="inlineStr">
+        <is>
+          <t>ЗЛАТИБОР</t>
+        </is>
+      </c>
+      <c r="E484" s="26" t="inlineStr">
+        <is>
+          <t>МИЛИНОВИЋ</t>
+        </is>
+      </c>
+      <c r="F484" s="26" t="inlineStr">
+        <is>
+          <t>065/784-018</t>
+        </is>
+      </c>
     </row>
     <row r="485" ht="18" customHeight="1">
       <c r="A485" s="26" t="inlineStr">
@@ -16023,22 +16087,22 @@
       </c>
       <c r="C506" s="26" t="inlineStr">
         <is>
-          <t>2802964143648</t>
+          <t>1305993105022</t>
         </is>
       </c>
       <c r="D506" s="26" t="inlineStr">
         <is>
-          <t>МИЛОJКО</t>
+          <t>ТАТJАНА</t>
         </is>
       </c>
       <c r="E506" s="26" t="inlineStr">
         <is>
-          <t>БАБИЋ</t>
+          <t>МАРКОВИЋ</t>
         </is>
       </c>
       <c r="F506" s="26" t="inlineStr">
         <is>
-          <t>065/789-765</t>
+          <t>066 358 945</t>
         </is>
       </c>
     </row>
@@ -16100,7 +16164,11 @@
           <t>МАСТАЛИЦА</t>
         </is>
       </c>
-      <c r="F508" s="26" t="n"/>
+      <c r="F508" s="26" t="inlineStr">
+        <is>
+          <t>066/829-097</t>
+        </is>
+      </c>
     </row>
     <row r="509" ht="18" customHeight="1">
       <c r="A509" s="26" t="inlineStr">
